--- a/diseases/d109/2000-2004.xlsx
+++ b/diseases/d109/2000-2004.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>28</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.5409372104235123</v>
       </c>
@@ -1388,9 +1385,6 @@
       <c r="O5" t="n">
         <v>9</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.2004067366056487</v>
       </c>
@@ -1784,9 +1778,6 @@
       <c r="O7" t="n">
         <v>25</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.4829796521638503</v>
       </c>
@@ -2407,9 +2398,6 @@
       <c r="O10" t="n">
         <v>7</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.1558719062488379</v>
       </c>
@@ -2803,9 +2791,6 @@
       <c r="O12" t="n">
         <v>15</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.2897877912983102</v>
       </c>
@@ -3426,9 +3411,6 @@
       <c r="O15" t="n">
         <v>2</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.04453483035681084</v>
       </c>
@@ -3822,9 +3804,6 @@
       <c r="O17" t="n">
         <v>22</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.4250220939041883</v>
       </c>
@@ -4445,9 +4424,6 @@
       <c r="O20" t="n">
         <v>9</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.2004067366056487</v>
       </c>
@@ -4841,9 +4817,6 @@
       <c r="O22" t="n">
         <v>51</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.9852784904142545</v>
       </c>
@@ -5464,9 +5437,6 @@
       <c r="O25" t="n">
         <v>5</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.1113370758920271</v>
       </c>
@@ -5860,9 +5830,6 @@
       <c r="O27" t="n">
         <v>72</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>1.390981398231889</v>
       </c>
@@ -6483,9 +6450,6 @@
       <c r="O30" t="n">
         <v>11</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.2449415669624596</v>
       </c>
@@ -6879,9 +6843,6 @@
       <c r="O32" t="n">
         <v>76</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>1.468258142578105</v>
       </c>
@@ -7502,9 +7463,6 @@
       <c r="O35" t="n">
         <v>13</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.2894763973192704</v>
       </c>
@@ -7898,9 +7856,6 @@
       <c r="O37" t="n">
         <v>138</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>2.666047679944453</v>
       </c>
@@ -8521,9 +8476,6 @@
       <c r="O40" t="n">
         <v>16</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.3562786428544867</v>
       </c>
@@ -8917,9 +8869,6 @@
       <c r="O42" t="n">
         <v>160</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>3.091069773848641</v>
       </c>
@@ -9540,9 +9489,6 @@
       <c r="O45" t="n">
         <v>21</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.4676157187465137</v>
       </c>
@@ -9936,9 +9882,6 @@
       <c r="O47" t="n">
         <v>136</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>2.627409307771345</v>
       </c>
@@ -10559,9 +10502,6 @@
       <c r="O50" t="n">
         <v>19</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.4230808883897029</v>
       </c>
@@ -10955,9 +10895,6 @@
       <c r="O52" t="n">
         <v>113</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>2.183068027780603</v>
       </c>
@@ -11578,9 +11515,6 @@
       <c r="O55" t="n">
         <v>15</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.3340112276760813</v>
       </c>
@@ -11974,9 +11908,6 @@
       <c r="O57" t="n">
         <v>55</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>1.062555234760471</v>
       </c>
@@ -12597,9 +12528,6 @@
       <c r="O60" t="n">
         <v>8</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.1781393214272433</v>
       </c>
@@ -12993,9 +12921,6 @@
       <c r="O62" t="n">
         <v>54</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>1.04086934950099</v>
       </c>
@@ -13616,9 +13541,6 @@
       <c r="O65" t="n">
         <v>12</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.2658598116782024</v>
       </c>
@@ -14012,9 +13934,6 @@
       <c r="O67" t="n">
         <v>35</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.6746375413432342</v>
       </c>
@@ -14635,9 +14554,6 @@
       <c r="O70" t="n">
         <v>10</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.2215498430651687</v>
       </c>
@@ -15031,9 +14947,6 @@
       <c r="O72" t="n">
         <v>38</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.7324636163155114</v>
       </c>
@@ -15654,9 +15567,6 @@
       <c r="O75" t="n">
         <v>10</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.2215498430651687</v>
       </c>
@@ -16050,9 +15960,6 @@
       <c r="O77" t="n">
         <v>30</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.5782607497227721</v>
       </c>
@@ -16673,9 +16580,6 @@
       <c r="O80" t="n">
         <v>7</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.1550848901456181</v>
       </c>
@@ -17069,9 +16973,6 @@
       <c r="O82" t="n">
         <v>38</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.7324636163155114</v>
       </c>
@@ -17692,9 +17593,6 @@
       <c r="O85" t="n">
         <v>4</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.08861993722606747</v>
       </c>
@@ -18088,9 +17986,6 @@
       <c r="O87" t="n">
         <v>42</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.8095650496118811</v>
       </c>
@@ -18711,9 +18606,6 @@
       <c r="O90" t="n">
         <v>7</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.1550848901456181</v>
       </c>
@@ -19107,9 +18999,6 @@
       <c r="O92" t="n">
         <v>56</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>1.079420066149175</v>
       </c>
@@ -19730,9 +19619,6 @@
       <c r="O95" t="n">
         <v>17</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.3766347332107867</v>
       </c>
@@ -20126,9 +20012,6 @@
       <c r="O97" t="n">
         <v>98</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>1.888985115761056</v>
       </c>
@@ -20749,9 +20632,6 @@
       <c r="O100" t="n">
         <v>16</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.3544797489042699</v>
       </c>
@@ -21145,9 +21025,6 @@
       <c r="O102" t="n">
         <v>91</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>1.754057607492409</v>
       </c>
@@ -21768,9 +21645,6 @@
       <c r="O105" t="n">
         <v>13</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.2880147959847193</v>
       </c>
@@ -22164,9 +22038,6 @@
       <c r="O107" t="n">
         <v>68</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>1.310724366038283</v>
       </c>
@@ -22787,9 +22658,6 @@
       <c r="O110" t="n">
         <v>17</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.3766347332107867</v>
       </c>
@@ -23183,9 +23051,6 @@
       <c r="O112" t="n">
         <v>84</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>1.619130099223762</v>
       </c>
@@ -23806,9 +23671,6 @@
       <c r="O115" t="n">
         <v>20</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.4430996861303373</v>
       </c>
@@ -24202,9 +24064,6 @@
       <c r="O117" t="n">
         <v>53</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>1.021593991176897</v>
       </c>
@@ -24825,9 +24684,6 @@
       <c r="O120" t="n">
         <v>7</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.1550848901456181</v>
       </c>
@@ -25221,9 +25077,6 @@
       <c r="O122" t="n">
         <v>69</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>1.326783764627791</v>
       </c>
@@ -25844,9 +25697,6 @@
       <c r="O125" t="n">
         <v>5</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.1101803564290458</v>
       </c>
@@ -26240,9 +26090,6 @@
       <c r="O127" t="n">
         <v>43</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.8268362591158698</v>
       </c>
@@ -26863,9 +26710,6 @@
       <c r="O130" t="n">
         <v>6</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.132216427714855</v>
       </c>
@@ -27259,9 +27103,6 @@
       <c r="O132" t="n">
         <v>50</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.9614375105998486</v>
       </c>
@@ -27882,9 +27723,6 @@
       <c r="O135" t="n">
         <v>4</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.08814428514323666</v>
       </c>
@@ -28278,9 +28116,6 @@
       <c r="O137" t="n">
         <v>52</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.9998950110238425</v>
       </c>
@@ -28901,9 +28736,6 @@
       <c r="O140" t="n">
         <v>1</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -29297,9 +29129,6 @@
       <c r="O142" t="n">
         <v>56</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>1.07681001187183</v>
       </c>
@@ -29920,9 +29749,6 @@
       <c r="O145" t="n">
         <v>3</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.0661082138574275</v>
       </c>
@@ -30316,9 +30142,6 @@
       <c r="O147" t="n">
         <v>64</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>1.230640013567806</v>
       </c>
@@ -30939,9 +30762,6 @@
       <c r="O150" t="n">
         <v>4</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.08814428514323666</v>
       </c>
@@ -31335,9 +31155,6 @@
       <c r="O152" t="n">
         <v>80</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>1.538300016959758</v>
       </c>
@@ -31958,9 +31775,6 @@
       <c r="O155" t="n">
         <v>12</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.26443285542971</v>
       </c>
@@ -32354,9 +32168,6 @@
       <c r="O157" t="n">
         <v>94</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>1.807502519927715</v>
       </c>
@@ -32977,9 +32788,6 @@
       <c r="O160" t="n">
         <v>16</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.3525771405729466</v>
       </c>
@@ -33373,9 +33181,6 @@
       <c r="O162" t="n">
         <v>127</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>2.442051276923615</v>
       </c>
@@ -33996,9 +33801,6 @@
       <c r="O165" t="n">
         <v>11</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.2423967841439008</v>
       </c>
@@ -34392,9 +34194,6 @@
       <c r="O167" t="n">
         <v>92</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>1.769045019503721</v>
       </c>
@@ -35015,9 +34814,6 @@
       <c r="O170" t="n">
         <v>20</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.4407214257161833</v>
       </c>
@@ -35411,9 +35207,6 @@
       <c r="O172" t="n">
         <v>84</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>1.615215017807746</v>
       </c>
@@ -36034,9 +35827,6 @@
       <c r="O175" t="n">
         <v>13</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.2864689267155192</v>
       </c>
@@ -36430,9 +36220,6 @@
       <c r="O177" t="n">
         <v>64</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>1.230640013567806</v>
       </c>
@@ -37053,9 +36840,6 @@
       <c r="O180" t="n">
         <v>8</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.1762885702864733</v>
       </c>
@@ -37449,9 +37233,6 @@
       <c r="O182" t="n">
         <v>58</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>1.112612711983894</v>
       </c>
@@ -38072,9 +37853,6 @@
       <c r="O185" t="n">
         <v>8</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.1752591480346111</v>
       </c>
@@ -38468,9 +38246,6 @@
       <c r="O187" t="n">
         <v>40</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.7673191117130302</v>
       </c>
@@ -39091,9 +38866,6 @@
       <c r="O190" t="n">
         <v>7</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.1533517545302847</v>
       </c>
@@ -39487,9 +39259,6 @@
       <c r="O192" t="n">
         <v>50</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.959148889641288</v>
       </c>
@@ -40110,9 +39879,6 @@
       <c r="O195" t="n">
         <v>5</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.1095369675216319</v>
       </c>
@@ -40506,9 +40272,6 @@
       <c r="O197" t="n">
         <v>54</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>1.035880800812591</v>
       </c>
@@ -41129,9 +40892,6 @@
       <c r="O200" t="n">
         <v>6</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.1314443610259583</v>
       </c>
@@ -41525,9 +41285,6 @@
       <c r="O202" t="n">
         <v>39</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0.7481361339202046</v>
       </c>
@@ -42148,9 +41905,6 @@
       <c r="O205" t="n">
         <v>3</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.06572218051297914</v>
       </c>
@@ -42544,9 +42298,6 @@
       <c r="O207" t="n">
         <v>50</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.959148889641288</v>
       </c>
@@ -43167,9 +42918,6 @@
       <c r="O210" t="n">
         <v>8</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.1752591480346111</v>
       </c>
@@ -43563,9 +43311,6 @@
       <c r="O212" t="n">
         <v>64</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>1.227710578740849</v>
       </c>
@@ -44186,9 +43931,6 @@
       <c r="O215" t="n">
         <v>17</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.3724256895735485</v>
       </c>
@@ -44582,9 +44324,6 @@
       <c r="O217" t="n">
         <v>85</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>1.63055311239019</v>
       </c>
@@ -45205,9 +44944,6 @@
       <c r="O220" t="n">
         <v>16</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.3505182960692221</v>
       </c>
@@ -45601,9 +45337,6 @@
       <c r="O222" t="n">
         <v>88</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>1.688102045768667</v>
       </c>
@@ -46224,9 +45957,6 @@
       <c r="O225" t="n">
         <v>22</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.4819626570951804</v>
       </c>
@@ -46620,9 +46350,6 @@
       <c r="O227" t="n">
         <v>97</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>1.860748845904099</v>
       </c>
@@ -47243,9 +46970,6 @@
       <c r="O230" t="n">
         <v>29</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.6353144116254651</v>
       </c>
@@ -47639,9 +47363,6 @@
       <c r="O232" t="n">
         <v>70</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>1.342808445497803</v>
       </c>
@@ -48262,9 +47983,6 @@
       <c r="O235" t="n">
         <v>15</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0.3286109025648957</v>
       </c>
@@ -48658,9 +48376,6 @@
       <c r="O237" t="n">
         <v>51</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0.9783318674341136</v>
       </c>
@@ -49281,9 +48996,6 @@
       <c r="O240" t="n">
         <v>13</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.284796115556243</v>
       </c>
@@ -49677,9 +49389,6 @@
       <c r="O242" t="n">
         <v>77</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>1.472796868030515</v>
       </c>
@@ -50300,9 +50009,6 @@
       <c r="O245" t="n">
         <v>6</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.1306693482920699</v>
       </c>
@@ -50696,9 +50402,6 @@
       <c r="O247" t="n">
         <v>53</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>1.013743298774251</v>
       </c>
@@ -51319,9 +51022,6 @@
       <c r="O250" t="n">
         <v>9</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.1960040224381049</v>
       </c>
@@ -51715,9 +51415,6 @@
       <c r="O252" t="n">
         <v>57</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>1.090252226983628</v>
       </c>
@@ -52338,9 +52035,6 @@
       <c r="O255" t="n">
         <v>7</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.152447573007415</v>
       </c>
@@ -52734,9 +52428,6 @@
       <c r="O257" t="n">
         <v>58</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>1.109379459035972</v>
       </c>
@@ -53357,9 +53048,6 @@
       <c r="O260" t="n">
         <v>1</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -53753,9 +53441,6 @@
       <c r="O262" t="n">
         <v>50</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.9563616026172175</v>
       </c>
@@ -54376,9 +54061,6 @@
       <c r="O265" t="n">
         <v>6</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0.1306693482920699</v>
       </c>
@@ -54772,9 +54454,6 @@
       <c r="O267" t="n">
         <v>71</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>1.358033475716449</v>
       </c>
@@ -55395,9 +55074,6 @@
       <c r="O270" t="n">
         <v>10</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0.2177822471534499</v>
       </c>
@@ -55791,9 +55467,6 @@
       <c r="O272" t="n">
         <v>95</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>1.817087044972713</v>
       </c>
@@ -56414,9 +56087,6 @@
       <c r="O275" t="n">
         <v>27</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.5880120673143148</v>
       </c>
@@ -56810,9 +56480,6 @@
       <c r="O277" t="n">
         <v>154</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>2.94559373606103</v>
       </c>
@@ -57433,9 +57100,6 @@
       <c r="O280" t="n">
         <v>55</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>1.197802359343975</v>
       </c>
@@ -57829,9 +57493,6 @@
       <c r="O282" t="n">
         <v>174</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>3.328138377107917</v>
       </c>
@@ -58452,9 +58113,6 @@
       <c r="O285" t="n">
         <v>43</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.9364636627598346</v>
       </c>
@@ -58848,9 +58506,6 @@
       <c r="O287" t="n">
         <v>114</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>2.180504453967256</v>
       </c>
@@ -59471,9 +59126,6 @@
       <c r="O290" t="n">
         <v>44</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0.9582418874751797</v>
       </c>
@@ -59867,9 +59519,6 @@
       <c r="O292" t="n">
         <v>144</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>2.754321415537586</v>
       </c>
@@ -60490,9 +60139,6 @@
       <c r="O295" t="n">
         <v>34</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.7404596403217297</v>
       </c>
@@ -60886,9 +60532,6 @@
       <c r="O297" t="n">
         <v>96</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>1.836214277025058</v>
       </c>
@@ -61508,9 +61151,6 @@
       </c>
       <c r="O300" t="n">
         <v>13</v>
-      </c>
-      <c r="Q300" t="n">
-        <v>0</v>
       </c>
       <c r="R300" t="n">
         <v>0.2831169212994849</v>

--- a/diseases/d109/2000-2004.xlsx
+++ b/diseases/d109/2000-2004.xlsx
@@ -1250,26 +1250,30 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1410,7 +1414,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1418,17 +1422,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1644,7 +1653,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1652,17 +1661,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2263,26 +2277,30 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2423,7 +2441,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2431,17 +2449,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2657,7 +2680,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2665,17 +2688,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -3276,26 +3304,30 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3436,7 +3468,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3444,17 +3476,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -3670,7 +3707,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -3678,17 +3715,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -4289,26 +4331,30 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -4449,7 +4495,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -4457,17 +4503,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -4683,7 +4734,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -4691,17 +4742,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -5302,26 +5358,30 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -5462,7 +5522,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -5470,17 +5530,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS25" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -5696,7 +5761,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -5704,17 +5769,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS26" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -6315,26 +6385,30 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -6475,7 +6549,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -6483,17 +6557,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS30" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -6709,7 +6788,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
@@ -6717,17 +6796,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS31" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -7328,26 +7412,30 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -7488,7 +7576,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
@@ -7496,17 +7584,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS35" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -7722,7 +7815,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -7730,17 +7823,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS36" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -8341,26 +8439,30 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -8501,7 +8603,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
@@ -8509,17 +8611,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS40" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -8735,7 +8842,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
@@ -8743,17 +8850,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS41" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -9354,26 +9466,30 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -9514,7 +9630,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -9522,17 +9638,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS45" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -9748,7 +9869,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -9756,17 +9877,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -10367,26 +10493,30 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -10527,7 +10657,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
@@ -10535,17 +10665,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS50" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -10761,7 +10896,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
@@ -10769,17 +10904,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS51" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -11380,26 +11520,30 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS54" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -11540,7 +11684,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
@@ -11548,17 +11692,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS55" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -11774,7 +11923,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
@@ -11782,17 +11931,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS56" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -12393,26 +12547,30 @@
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -12553,7 +12711,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
@@ -12561,17 +12719,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS60" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -12787,7 +12950,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
@@ -12795,17 +12958,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS61" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -13406,26 +13574,30 @@
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS64" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -13566,7 +13738,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
@@ -13574,17 +13746,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS65" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -13800,7 +13977,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
@@ -13808,17 +13985,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS66" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -14419,26 +14601,30 @@
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS69" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -14579,7 +14765,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -14587,17 +14773,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS70" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -14813,7 +15004,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
@@ -14821,17 +15012,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS71" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -15432,26 +15628,30 @@
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -15592,7 +15792,7 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
@@ -15600,17 +15800,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS75" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
@@ -15826,7 +16031,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
@@ -15834,17 +16039,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS76" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -16445,26 +16655,30 @@
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -16605,7 +16819,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
@@ -16613,17 +16827,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS80" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -16839,7 +17058,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
@@ -16847,17 +17066,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS81" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -17458,26 +17682,30 @@
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -17618,7 +17846,7 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ85" t="inlineStr">
@@ -17626,17 +17854,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS85" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -17852,7 +18085,7 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
@@ -17860,17 +18093,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS86" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -18471,26 +18709,30 @@
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -18631,7 +18873,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
@@ -18639,17 +18881,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS90" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -18865,7 +19112,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
@@ -18873,17 +19120,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS91" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
@@ -19484,26 +19736,30 @@
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -19644,7 +19900,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
@@ -19652,17 +19908,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS95" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -19878,7 +20139,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
@@ -19886,17 +20147,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS96" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -20497,26 +20763,30 @@
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -20657,7 +20927,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ100" t="inlineStr">
@@ -20665,17 +20935,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS100" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -20891,7 +21166,7 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ101" t="inlineStr">
@@ -20899,17 +21174,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS101" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -21510,26 +21790,30 @@
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -21670,7 +21954,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
@@ -21678,17 +21962,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS105" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -21904,7 +22193,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
@@ -21912,17 +22201,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS106" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -22523,26 +22817,30 @@
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -22683,7 +22981,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
@@ -22691,17 +22989,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS110" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -22917,7 +23220,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
@@ -22925,17 +23228,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS111" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -23536,26 +23844,30 @@
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -23696,7 +24008,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
@@ -23704,17 +24016,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS115" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -23930,7 +24247,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
@@ -23938,17 +24255,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS116" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -24549,26 +24871,30 @@
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -24709,7 +25035,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
@@ -24717,17 +25043,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS120" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -24943,7 +25274,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
@@ -24951,17 +25282,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS121" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -25562,26 +25898,30 @@
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ124" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
@@ -25722,7 +26062,7 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ125" t="inlineStr">
@@ -25730,17 +26070,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS125" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -25956,7 +26301,7 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
@@ -25964,17 +26309,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS126" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
@@ -26575,26 +26925,30 @@
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
@@ -26735,7 +27089,7 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
@@ -26743,17 +27097,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS130" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -26969,7 +27328,7 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
@@ -26977,17 +27336,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS131" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -27588,26 +27952,30 @@
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
@@ -27748,7 +28116,7 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
@@ -27756,17 +28124,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS135" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
@@ -27982,7 +28355,7 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
@@ -27990,17 +28363,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS136" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
@@ -28601,26 +28979,30 @@
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ139" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
@@ -28761,7 +29143,7 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ140" t="inlineStr">
@@ -28769,17 +29151,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS140" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
@@ -28995,7 +29382,7 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
@@ -29003,17 +29390,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS141" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -29614,26 +30006,30 @@
       </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ144" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
@@ -29774,7 +30170,7 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
@@ -29782,17 +30178,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS145" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
@@ -30008,7 +30409,7 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
@@ -30016,17 +30417,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS146" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
@@ -30627,26 +31033,30 @@
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ149" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
@@ -30787,7 +31197,7 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
@@ -30795,17 +31205,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS150" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
@@ -31021,7 +31436,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
@@ -31029,17 +31444,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS151" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
@@ -31640,26 +32060,30 @@
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ154" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
@@ -31800,7 +32224,7 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
@@ -31808,17 +32232,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS155" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
@@ -32034,7 +32463,7 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
@@ -32042,17 +32471,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS156" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
@@ -32653,26 +33087,30 @@
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ159" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
@@ -32813,7 +33251,7 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ160" t="inlineStr">
@@ -32821,17 +33259,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS160" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
@@ -33047,7 +33490,7 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ161" t="inlineStr">
@@ -33055,17 +33498,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS161" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
@@ -33666,26 +34114,30 @@
       </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ164" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
@@ -33826,7 +34278,7 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ165" t="inlineStr">
@@ -33834,17 +34286,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS165" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
@@ -34060,7 +34517,7 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ166" t="inlineStr">
@@ -34068,17 +34525,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS166" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
@@ -34679,26 +35141,30 @@
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ169" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
@@ -34839,7 +35305,7 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ170" t="inlineStr">
@@ -34847,17 +35313,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS170" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
@@ -35073,7 +35544,7 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ171" t="inlineStr">
@@ -35081,17 +35552,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS171" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
@@ -35692,26 +36168,30 @@
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
@@ -35852,7 +36332,7 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
@@ -35860,17 +36340,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS175" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -36086,7 +36571,7 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ176" t="inlineStr">
@@ -36094,17 +36579,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS176" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
@@ -36705,26 +37195,30 @@
       </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ179" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
@@ -36865,7 +37359,7 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ180" t="inlineStr">
@@ -36873,17 +37367,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS180" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
@@ -37099,7 +37598,7 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ181" t="inlineStr">
@@ -37107,17 +37606,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS181" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
@@ -37718,26 +38222,30 @@
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ184" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
@@ -37878,7 +38386,7 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ185" t="inlineStr">
@@ -37886,17 +38394,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS185" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
@@ -38112,7 +38625,7 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ186" t="inlineStr">
@@ -38120,17 +38633,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS186" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
@@ -38731,26 +39249,30 @@
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ189" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
@@ -38891,7 +39413,7 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ190" t="inlineStr">
@@ -38899,17 +39421,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS190" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
@@ -39125,7 +39652,7 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ191" t="inlineStr">
@@ -39133,17 +39660,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS191" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
@@ -39744,26 +40276,30 @@
       </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ194" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT194" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
@@ -39904,7 +40440,7 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ195" t="inlineStr">
@@ -39912,17 +40448,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS195" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
@@ -40138,7 +40679,7 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ196" t="inlineStr">
@@ -40146,17 +40687,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS196" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
@@ -40757,26 +41303,30 @@
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
@@ -40917,7 +41467,7 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
@@ -40925,17 +41475,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS200" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
@@ -41151,7 +41706,7 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
@@ -41159,17 +41714,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS201" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
@@ -41770,26 +42330,30 @@
       </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ204" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
@@ -41930,7 +42494,7 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ205" t="inlineStr">
@@ -41938,17 +42502,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS205" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
@@ -42164,7 +42733,7 @@
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ206" t="inlineStr">
@@ -42172,17 +42741,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS206" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
@@ -42783,26 +43357,30 @@
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ209" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
@@ -42943,7 +43521,7 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ210" t="inlineStr">
@@ -42951,17 +43529,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS210" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
@@ -43177,7 +43760,7 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ211" t="inlineStr">
@@ -43185,17 +43768,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS211" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
@@ -43796,26 +44384,30 @@
       </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ214" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS214" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT214" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
@@ -43956,7 +44548,7 @@
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ215" t="inlineStr">
@@ -43964,17 +44556,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS215" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
@@ -44190,7 +44787,7 @@
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ216" t="inlineStr">
@@ -44198,17 +44795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS216" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
@@ -44809,26 +45411,30 @@
       </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ219" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS219" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
@@ -44969,7 +45575,7 @@
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ220" t="inlineStr">
@@ -44977,17 +45583,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS220" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
@@ -45203,7 +45814,7 @@
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ221" t="inlineStr">
@@ -45211,17 +45822,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR221" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS221" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
@@ -45822,26 +46438,30 @@
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS224" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT224" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
@@ -45982,7 +46602,7 @@
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
@@ -45990,17 +46610,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS225" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
@@ -46216,7 +46841,7 @@
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
@@ -46224,17 +46849,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS226" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
@@ -46835,26 +47465,30 @@
       </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ229" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS229" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT229" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
@@ -46995,7 +47629,7 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ230" t="inlineStr">
@@ -47003,17 +47637,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS230" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
@@ -47229,7 +47868,7 @@
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
@@ -47237,17 +47876,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS231" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
@@ -47848,26 +48492,30 @@
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ234" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
@@ -48008,7 +48656,7 @@
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ235" t="inlineStr">
@@ -48016,17 +48664,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR235" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS235" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
@@ -48242,7 +48895,7 @@
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ236" t="inlineStr">
@@ -48250,17 +48903,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS236" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
@@ -48861,26 +49519,30 @@
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ239" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
@@ -49021,7 +49683,7 @@
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ240" t="inlineStr">
@@ -49029,17 +49691,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS240" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
@@ -49255,7 +49922,7 @@
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ241" t="inlineStr">
@@ -49263,17 +49930,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR241" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS241" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT241" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
@@ -49874,26 +50546,30 @@
       </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ244" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS244" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
@@ -50034,7 +50710,7 @@
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ245" t="inlineStr">
@@ -50042,17 +50718,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR245" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS245" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
@@ -50268,7 +50949,7 @@
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ246" t="inlineStr">
@@ -50276,17 +50957,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS246" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
@@ -50887,26 +51573,30 @@
       </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ249" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
@@ -51047,7 +51737,7 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ250" t="inlineStr">
@@ -51055,17 +51745,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS250" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
@@ -51281,7 +51976,7 @@
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ251" t="inlineStr">
@@ -51289,17 +51984,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS251" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
@@ -51900,26 +52600,30 @@
       </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ254" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT254" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
@@ -52060,7 +52764,7 @@
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ255" t="inlineStr">
@@ -52068,17 +52772,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS255" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
@@ -52294,7 +53003,7 @@
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ256" t="inlineStr">
@@ -52302,17 +53011,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS256" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
@@ -52913,26 +53627,30 @@
       </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ259" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS259" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT259" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
@@ -53073,7 +53791,7 @@
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ260" t="inlineStr">
@@ -53081,17 +53799,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS260" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
@@ -53307,7 +54030,7 @@
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ261" t="inlineStr">
@@ -53315,17 +54038,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS261" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
@@ -53926,26 +54654,30 @@
       </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ264" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS264" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT264" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
@@ -54086,7 +54818,7 @@
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ265" t="inlineStr">
@@ -54094,17 +54826,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS265" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
@@ -54320,7 +55057,7 @@
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ266" t="inlineStr">
@@ -54328,17 +55065,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR266" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS266" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
@@ -54939,26 +55681,30 @@
       </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ269" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT269" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
@@ -55099,7 +55845,7 @@
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ270" t="inlineStr">
@@ -55107,17 +55853,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS270" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT270" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
@@ -55333,7 +56084,7 @@
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ271" t="inlineStr">
@@ -55341,17 +56092,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS271" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
@@ -55952,26 +56708,30 @@
       </c>
       <c r="AO274" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ274" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS274" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV274" t="inlineStr">
@@ -56112,7 +56872,7 @@
       </c>
       <c r="AP275" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ275" t="inlineStr">
@@ -56120,17 +56880,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR275" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS275" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV275" t="inlineStr">
@@ -56346,7 +57111,7 @@
       </c>
       <c r="AP276" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ276" t="inlineStr">
@@ -56354,17 +57119,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR276" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS276" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV276" t="inlineStr">
@@ -56965,26 +57735,30 @@
       </c>
       <c r="AO279" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ279" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS279" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV279" t="inlineStr">
@@ -57125,7 +57899,7 @@
       </c>
       <c r="AP280" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ280" t="inlineStr">
@@ -57133,17 +57907,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS280" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV280" t="inlineStr">
@@ -57359,7 +58138,7 @@
       </c>
       <c r="AP281" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ281" t="inlineStr">
@@ -57367,17 +58146,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR281" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS281" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV281" t="inlineStr">
@@ -57978,26 +58762,30 @@
       </c>
       <c r="AO284" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP284" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ284" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS284" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT284" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU284" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV284" t="inlineStr">
@@ -58138,7 +58926,7 @@
       </c>
       <c r="AP285" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ285" t="inlineStr">
@@ -58146,17 +58934,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR285" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS285" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT285" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV285" t="inlineStr">
@@ -58372,7 +59165,7 @@
       </c>
       <c r="AP286" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ286" t="inlineStr">
@@ -58380,17 +59173,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR286" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS286" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV286" t="inlineStr">
@@ -58991,26 +59789,30 @@
       </c>
       <c r="AO289" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP289" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ289" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS289" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS289" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT289" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV289" t="inlineStr">
@@ -59151,7 +59953,7 @@
       </c>
       <c r="AP290" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ290" t="inlineStr">
@@ -59159,17 +59961,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR290" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS290" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV290" t="inlineStr">
@@ -59385,7 +60192,7 @@
       </c>
       <c r="AP291" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ291" t="inlineStr">
@@ -59393,17 +60200,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR291" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS291" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT291" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU291" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV291" t="inlineStr">
@@ -60004,26 +60816,30 @@
       </c>
       <c r="AO294" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP294" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ294" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS294" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS294" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT294" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU294" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV294" t="inlineStr">
@@ -60164,7 +60980,7 @@
       </c>
       <c r="AP295" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ295" t="inlineStr">
@@ -60172,17 +60988,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR295" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS295" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT295" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU295" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV295" t="inlineStr">
@@ -60398,7 +61219,7 @@
       </c>
       <c r="AP296" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ296" t="inlineStr">
@@ -60406,17 +61227,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR296" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS296" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT296" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU296" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV296" t="inlineStr">
@@ -61017,26 +61843,30 @@
       </c>
       <c r="AO299" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP299" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ299" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS299" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS299" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_LYMENEURO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV299" t="inlineStr">
@@ -61177,7 +62007,7 @@
       </c>
       <c r="AP300" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ300" t="inlineStr">
@@ -61185,17 +62015,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR300" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS300" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV300" t="inlineStr">
@@ -61411,7 +62246,7 @@
       </c>
       <c r="AP301" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ301" t="inlineStr">
@@ -61419,17 +62254,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR301" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS301" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT301" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV301" t="inlineStr">
